--- a/calculatie/projecten/kioti-2/offerteregels.xlsx
+++ b/calculatie/projecten/kioti-2/offerteregels.xlsx
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L96" s="11">
         <f>SUM(L2:L94)</f>
-        <v/>
+        <v>359654.95</v>
       </c>
     </row>
   </sheetData>
